--- a/報價單範本.xlsx
+++ b/報價單範本.xlsx
@@ -1,249 +1,1049 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10621"/>
+  <workbookPr showInkAnnotation="0" checkCompatibility="1" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenpinyu/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F377BAB-0DF0-104E-B0E9-0F357B72F830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2320" yWindow="760" windowWidth="22140" windowHeight="16420" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="2320" yWindow="760" windowWidth="22140" windowHeight="16420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2026報價" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026報價" sheetId="30" r:id="rId1"/>
+    <sheet name="1060119" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="計算" sheetId="5" state="hidden" r:id="rId3"/>
+    <sheet name="決標後主項" sheetId="7" state="hidden" r:id="rId4"/>
+    <sheet name="決標後細項" sheetId="6" state="hidden" r:id="rId5"/>
+    <sheet name="驗證" sheetId="8" state="hidden" r:id="rId6"/>
+    <sheet name="EIP參考" sheetId="4" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'2026報價'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2026報價'!$A$1:$G$30</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr defaultImageDpi="330"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
+      <mx:ArchID Flags="2"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="177">
+  <si>
+    <t>項次</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>品項</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>數量</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>單價</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>一、</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1式</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>系統功能運作維運（系統異常排除、程式錯誤修正）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>總價(含稅)：</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>教育訓練</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>系統維運</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1式</t>
+  </si>
+  <si>
+    <t>1式</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="標楷體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>二</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="標楷體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>系統及資料維運作業（文化部及所屬17機關）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>4場</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>獎補助系統管理功能改版擴充</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>前臺</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>後台</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能分類</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRE-ORDER &amp; Quotation</t>
+  </si>
+  <si>
+    <t>致：</t>
+  </si>
+  <si>
+    <t>文化部</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>估價編號：</t>
+  </si>
+  <si>
+    <t>單位：</t>
+  </si>
+  <si>
+    <t>新台幣</t>
+  </si>
+  <si>
+    <t>有效期限：</t>
+  </si>
+  <si>
+    <r>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="標楷體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>天</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>前臺網站改版建置</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用者界面改版設計</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>RWD響應式網站設計( 首頁、內容頁、會員管理等)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>線上申請/報名功能擴充</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>獎補助訊息主動通知 - 帳號密碼管理功能功能調整</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>要點分類</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>會員功能擴充</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>程式版本維護管理</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>民眾互動及重要資訊呈現   
+-顯示報名中要點
+-評審委員名單
+-相關後端上架資訊
+-獎補助申請之教學流程</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>獎補助要點表單維運、新增、調整與諮詢</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>線上報名/申請機制維護</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>內、外部介接維護</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>推廣、輔導各機關辦理線上報名</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>客服輔導
+-客戶問題處理與回覆
+-客戶問題記錄與整理
+-會員資料整併更新
+-程式版本更新說明</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">資訊透明
+-審計查帳管理    
+-案件審核管理    
+-名單發佈機制  </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">系統管理架構調整及功能擴充  </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>系統架構調整 
+-欄位調整、欄位檢核。依受理日期控管各機關資料,產生報表(要點生命週期的時間來查核)
+-前臺資訊呈現與連結。
+-要點功能調整（類別、表單、範本等）
+-前臺資訊上架管理</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>案件審查管理機制</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">年度案件鎖定、變更及刪除與統計功能(特定使用者變更）  </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>受補助單位資訊查詢功能</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">報表功能擴充及活動成果功能擴充  </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>資料圖表統計功能</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他
+-綜合規劃司(資料統計及匯出)  
+-配合國發會CGSS擴充欄位
+-文化統計報表欄位建立及介接</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>20170119_mocgrant_v3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>說明</t>
+  </si>
+  <si>
+    <t>專案管理</t>
+  </si>
+  <si>
+    <t>(PM)</t>
+  </si>
+  <si>
+    <t>分析企劃</t>
+  </si>
+  <si>
+    <t>(SA)</t>
+  </si>
+  <si>
+    <t>程式設計</t>
+  </si>
+  <si>
+    <t>(PG)</t>
+  </si>
+  <si>
+    <t>小計</t>
+  </si>
+  <si>
+    <t>工作時數</t>
+  </si>
+  <si>
+    <t>時薪單價</t>
+  </si>
+  <si>
+    <t>時薪</t>
+  </si>
+  <si>
+    <t>單價</t>
+  </si>
+  <si>
+    <t>系統維護服務作業</t>
+  </si>
+  <si>
+    <t>提供各機關定期與不定期維護服務或問題諮詢</t>
+  </si>
+  <si>
+    <t>系統功能需求項目</t>
+  </si>
+  <si>
+    <r>
+      <t>媒體公關組</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="標楷體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>本部暨所屬行事曆功能擴充（增加欄位及產出報表）</t>
+    </r>
+  </si>
+  <si>
+    <t>國會聯絡管理系統表單新增修改</t>
+  </si>
+  <si>
+    <r>
+      <t>工藝中心表單新增修改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="標楷體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>赴大陸申請單）</t>
+    </r>
+  </si>
+  <si>
+    <t>資源分享專區功能擴充（分享專區）</t>
+  </si>
+  <si>
+    <t>需求變更表單與分派功能擴充</t>
+  </si>
+  <si>
+    <t>人權館的會議室資訊整合至本館行事曆</t>
+  </si>
+  <si>
+    <t>活動報名功能增加功能選項</t>
+  </si>
+  <si>
+    <t>報價金額總計</t>
+  </si>
+  <si>
+    <t>工時</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>小計</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">單價 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>專案管理</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>分析企劃</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>程式設計</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>分類</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>系統
+維運</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>教育訓練（4場）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>經費總計</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用者界面改版設計
+- 民眾互動及重要資訊呈現:顯示報名中要點/評審委員名單/相關後端上架資訊/獎補助申請之教學流程
+- 要點分類
+- 會員功能擴充
+- 線上申請/報名功能擴充
+- 獎補助訊息主動通知 - 帳號密碼管理功能功能調整</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">年度案件關檔鎖定(特定使用者變更）  </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用者帳號權限新增異動申請單</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>配合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> CGSS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="標楷體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>擴充功能</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>其它本案擴充功能
+－查詢團隊歷史案件部分欄位資訊
+－文化統計報表欄位建立及介接
+－擴充獎補助案件資料統計功能</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>項次</t>
+  </si>
+  <si>
+    <t>品項</t>
+  </si>
+  <si>
+    <t>數量</t>
+  </si>
+  <si>
+    <t>分類</t>
+  </si>
+  <si>
+    <t>工時</t>
+  </si>
+  <si>
+    <t xml:space="preserve">單價 </t>
+  </si>
+  <si>
+    <t>一、</t>
+  </si>
+  <si>
+    <t>系統及資料維運作業（文化部及所屬17機關）</t>
+  </si>
+  <si>
+    <t>系統</t>
+  </si>
+  <si>
+    <t>維運</t>
+  </si>
+  <si>
+    <t>系統功能運作維運（系統異常排除、程式錯誤修正）</t>
+  </si>
+  <si>
+    <t>獎補助要點表單維運、新增、調整與諮詢</t>
+  </si>
+  <si>
+    <t>線上報名/申請機制維護</t>
+  </si>
+  <si>
+    <t>推廣、輔導各機關辦理線上報名</t>
+  </si>
+  <si>
+    <t>內、外部介接維護</t>
+  </si>
+  <si>
+    <t>教育訓練（4場）</t>
+  </si>
+  <si>
+    <t>客服輔導</t>
+  </si>
+  <si>
+    <t>-客戶問題處理與回覆</t>
+  </si>
+  <si>
+    <t>-客戶問題記錄與整理</t>
+  </si>
+  <si>
+    <t>-會員資料整併更新</t>
+  </si>
+  <si>
+    <t>-程式版本更新說明</t>
+  </si>
+  <si>
+    <t>二、</t>
+  </si>
+  <si>
+    <t>獎補助系統管理功能改版擴充</t>
+  </si>
+  <si>
+    <t>前臺網站改版建置</t>
+  </si>
+  <si>
+    <t>前臺</t>
+  </si>
+  <si>
+    <t>使用者界面改版設計</t>
+  </si>
+  <si>
+    <t>- 民眾互動及重要資訊呈現:顯示報名中要點/評審委員名單/相關後端上架資訊/獎補助申請之教學流程</t>
+  </si>
+  <si>
+    <t>- 要點分類</t>
+  </si>
+  <si>
+    <t>- 會員功能擴充</t>
+  </si>
+  <si>
+    <t>- 線上申請/報名功能擴充</t>
+  </si>
+  <si>
+    <t>- 獎補助訊息主動通知 - 帳號密碼管理功能功能調整</t>
+  </si>
+  <si>
+    <t>RWD響應式網站設計( 首頁、內容頁、會員管理等)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">系統管理架構調整及功能擴充  </t>
+  </si>
+  <si>
+    <t>後台</t>
+  </si>
+  <si>
+    <t>系統架構調整</t>
+  </si>
+  <si>
+    <t>-欄位調整、欄位檢核。依受理日期控管各機關資料,產生報表(要點生命週期的時間來查核)</t>
+  </si>
+  <si>
+    <t>-前臺資訊呈現與連結。</t>
+  </si>
+  <si>
+    <t>-要點功能調整（類別、表單、範本等）</t>
+  </si>
+  <si>
+    <t>-前臺資訊上架管理</t>
+  </si>
+  <si>
+    <t>案件審查管理機制</t>
+  </si>
+  <si>
+    <t>程式版本維護管理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年度案件關檔鎖定(特定使用者變更）  </t>
+  </si>
+  <si>
+    <t>使用者帳號權限新增異動申請單</t>
+  </si>
+  <si>
+    <r>
+      <t>配合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> CGSS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="標楷體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>擴充功能</t>
+    </r>
+  </si>
+  <si>
+    <t>其它本案擴充功能</t>
+  </si>
+  <si>
+    <t>－查詢團隊歷史案件部分欄位資訊</t>
+  </si>
+  <si>
+    <t>－文化統計報表欄位建立及介接</t>
+  </si>
+  <si>
+    <t>－擴充獎補助案件資料統計功能</t>
+  </si>
+  <si>
+    <t>經費總計</t>
+  </si>
+  <si>
+    <t>維運總計</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>擴充總計</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>聯絡人：</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>估價編號：</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>項次</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註：</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>總價(含稅)：</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>以下空白</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>總價</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>以上單項報價均為含稅價。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>數量</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>單位</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司底價</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>********** 估    價    單 **********</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEL：</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>估價日期：</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>致       ：</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>有效日期：</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>承辦業務：</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>E-Mail   ：</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>FAX：</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>品名</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>總金額： 新台幣</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>元整</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2)ProxyOne Wildcard SSL憑證自動更新服務</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>付款方式：依雙方合約。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)ProxyOne網域名稱服務
+( Domain Name：*.proxyone****.flysheet.com.tw )</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ProxyOne Plus升級服務-SSL 憑證自動更新服務 </t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>林口長庚醫院圖書館</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>林定芳 小姐</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>(03)328-1200 ext 3464</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>CGMH_1150721</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>115年07月21日</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>115年07月31日</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>訂期:115/07/15-116/07/14</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳品伃</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>emilychen@flysheet.com.tw</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-26582223#113</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="167" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="[DBNum2][$-404]General"/>
-    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="8">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="[DBNum2][$-404]General"/>
   </numFmts>
   <fonts count="32">
     <font>
+      <sz val="12"/>
       <name val="新細明體"/>
       <charset val="136"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="新細明體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="新細明體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="新細明體"/>
+      <family val="3"/>
       <charset val="136"/>
-      <family val="3"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="標楷體"/>
+      <family val="3"/>
       <charset val="136"/>
-      <family val="3"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="新細明體"/>
+      <family val="3"/>
       <charset val="136"/>
-      <family val="3"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
       <name val="標楷體"/>
+      <family val="3"/>
       <charset val="136"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="11"/>
       <name val="新細明體"/>
+      <family val="3"/>
       <charset val="136"/>
-      <family val="3"/>
-      <color theme="11"/>
-      <sz val="12"/>
-      <u val="single"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
       <name val="標楷體"/>
+      <family val="4"/>
       <charset val="136"/>
-      <family val="4"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="新細明體"/>
+      <family val="3"/>
       <charset val="136"/>
-      <family val="3"/>
-      <color theme="10"/>
-      <sz val="12"/>
-      <u val="single"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="新細明體"/>
+      <family val="3"/>
       <charset val="136"/>
-      <family val="3"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="18"/>
       <name val="Copperplate Gothic Bold"/>
       <family val="2"/>
-      <sz val="18"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="標楷體"/>
+      <family val="3"/>
       <charset val="136"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="14"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
       <name val="標楷體"/>
+      <family val="3"/>
       <charset val="136"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="14"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <b val="1"/>
-      <sz val="14"/>
     </font>
     <font>
+      <sz val="14"/>
       <name val="標楷體"/>
+      <family val="3"/>
       <charset val="136"/>
-      <family val="3"/>
-      <sz val="14"/>
     </font>
     <font>
+      <sz val="14"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="14"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
       <name val="新細明體"/>
+      <family val="3"/>
       <charset val="136"/>
-      <family val="3"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
-      <family val="1"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
-      <family val="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
-      <family val="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="16"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <sz val="16"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF333333"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="12"/>
-      <u val="single"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
     <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
-      <family val="1"/>
-      <color theme="10"/>
-      <sz val="12"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -256,7 +1056,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7999816888943144"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -268,18 +1068,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.3499862666707358"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="65">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -914,953 +1714,1728 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="double">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="double">
-        <color auto="1"/>
-      </right>
-      <top style="double">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="double">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="double">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="double">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="15">
+  <cellStyleXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="177" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="233">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="223">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="6" fontId="6" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="17" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="17" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="17" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="18" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="114" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="114" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="114" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" xfId="114" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="117">
+    <xf numFmtId="179" fontId="22" fillId="0" borderId="0" xfId="117" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="117">
+    <xf numFmtId="179" fontId="22" fillId="0" borderId="0" xfId="117" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="115">
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="0" xfId="115" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="115">
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="0" xfId="115" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="114" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="114" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="116">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="116" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="114" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="23" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="114" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="114" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="114" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="180" fontId="30" fillId="0" borderId="0" xfId="114" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="23" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="114" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="114" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="114" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="114" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="114" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="118">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="118" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="114" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="114" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="23" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="23" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="117">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="117">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="115">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="114">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="15">
+  <cellStyles count="119">
+    <cellStyle name="0,0_x000d__x000d_NA_x000d__x000d_" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="一般_飛資得系統科技_德霖技術學院Aleph報價單990910" xfId="1"/>
-    <cellStyle name="0,0_x000d__x000d_NA_x000d__x000d_" xfId="2"/>
-    <cellStyle name="一般 2" xfId="3"/>
+    <cellStyle name="一般 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="一般 3" xfId="109" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="一般 4" xfId="110" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="一般 5" xfId="113" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="一般 6" xfId="114" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="一般_飛資得系統科技_德霖技術學院Aleph報價單990910" xfId="1" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="一般_飛資得系統科技_德霖技術學院Aleph報價單990910 2" xfId="116" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="千分位[0] 2" xfId="115" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
     <cellStyle name="已瀏覽過的超連結" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="超連結" xfId="5" builtinId="8" hidden="1"/>
-    <cellStyle name="一般 3" xfId="6"/>
-    <cellStyle name="一般 4" xfId="7"/>
-    <cellStyle name="貨幣 2" xfId="8"/>
-    <cellStyle name="百分比 2" xfId="9"/>
-    <cellStyle name="一般 5" xfId="10"/>
-    <cellStyle name="一般 6" xfId="11"/>
-    <cellStyle name="千分位[0] 2" xfId="12"/>
-    <cellStyle name="一般_飛資得系統科技_德霖技術學院Aleph報價單990910 2" xfId="13"/>
-    <cellStyle name="貨幣" xfId="14" builtinId="4"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="5" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="7" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="8" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="9" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="10" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="11" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="12" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="13" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="14" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="15" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="16" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="17" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="18" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="19" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="20" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="21" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="22" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="23" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="24" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="25" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="26" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="27" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="28" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="29" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="30" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="31" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="32" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="33" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="34" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="35" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="36" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="37" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="38" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="39" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="40" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="41" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="42" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="43" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="44" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="45" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="46" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="47" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="48" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="50" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="52" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="54" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="56" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="58" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="60" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="62" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="64" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="66" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="68" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="70" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="72" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="74" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="76" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="78" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="80" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="82" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="84" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="86" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="88" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="90" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="92" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="94" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="96" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="98" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="100" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="102" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="104" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="106" builtinId="9" hidden="1"/>
+    <cellStyle name="已瀏覽過的超連結" xfId="108" builtinId="9" hidden="1"/>
+    <cellStyle name="百分比 2" xfId="112" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="貨幣" xfId="117" builtinId="4"/>
+    <cellStyle name="貨幣 2" xfId="111" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="超連結" xfId="49" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="51" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="53" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="55" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="57" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="59" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="61" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="63" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="65" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="67" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="69" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="71" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="73" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="75" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="77" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="79" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="81" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="83" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="85" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="87" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="89" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="91" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="93" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="95" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="97" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="99" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="101" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="103" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="105" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="107" builtinId="8" hidden="1"/>
+    <cellStyle name="超連結" xfId="118" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>16520</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>149563</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>711695</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>152559</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="圖片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B00D5EF6-80D6-32C7-35F7-2EB136C44ECA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5131603" y="24419894"/>
+          <a:ext cx="1828800" cy="1270000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3108156</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>200527</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>924647</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>89123</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Text Box 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B65C679A-1246-139C-B8B9-D2C51E353140}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeAspect="1" noEditPoints="1" noChangeArrowheads="1" noChangeShapeType="1" noTextEdit="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3899121" y="200527"/>
+          <a:ext cx="3397807" cy="1158596"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+          <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+            <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:effectLst/>
+            </a14:hiddenEffects>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr rot="0" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="t" anchorCtr="0" upright="1">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1050" kern="100">
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t>FlySheet Med-Informatics Co., Ltd                </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1050" kern="100">
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t>114</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-TW" sz="1050" kern="100">
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t>臺北市內湖區內湖路一段</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1050" kern="100">
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t>91</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-TW" sz="1050" kern="100">
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t>巷</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1050" kern="100">
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t>40</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-TW" sz="1050" kern="100">
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t>號</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1050" kern="100">
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t>2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-TW" sz="1050" kern="100">
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t>樓</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-TW" sz="1200" kern="100">
+            <a:effectLst/>
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:ea typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1050" kern="100">
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t>2F, No. 40, Lane. 91, Sec1, NeiHu .Rd, Taipei, Taiwan, R.O.C.</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-TW" sz="1200" kern="100">
+            <a:effectLst/>
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:ea typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1050" kern="100">
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t>TEL: 886-2-2658-2223   FAX: 886-2-2658-2224</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-TW" sz="1200" kern="100">
+            <a:effectLst/>
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:ea typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1050" u="none" strike="noStrike" kern="100">
+              <a:solidFill>
+                <a:srgbClr val="0000FF"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t>URL: http://www.flysheet.com.tw</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-TW" sz="1200" kern="100">
+            <a:effectLst/>
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:ea typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="zh-TW" sz="1050" kern="100">
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t>統一編號：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1050" kern="100">
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="標楷體"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t>24309020</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-TW" sz="1200" kern="100">
+            <a:effectLst/>
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:ea typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" kern="100">
+              <a:effectLst/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+              <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-TW" sz="1200" kern="100">
+            <a:effectLst/>
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:ea typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+            <a:cs typeface="新細明體" panose="02020500000000000000" pitchFamily="18" charset="-120"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>181775</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>219156</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2863070</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>154395</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="圖片 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6E6D75C-F66A-3E9E-39A6-DB8638B9BF4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="181775" y="219156"/>
+          <a:ext cx="3472260" cy="547958"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>11140</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>100325</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3832281" cy="580159"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="文字方塊 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{913693E9-9A87-56D1-CA81-3E5B37F3C765}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11140" y="713044"/>
+          <a:ext cx="3832281" cy="580159"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="zh-TW" altLang="zh-TW" sz="2200">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>飛資得醫學資訊股份有限公司</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1079500</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>109855</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>145204</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="圖片 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A863DB75-3774-1197-5A41-772EAE1C6B22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5194300" y="8089900"/>
+          <a:ext cx="1900555" cy="1144270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>5080</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>106045</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>102870</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>106045</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="直線接點 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4752F33-80DA-EA2B-07A0-470A4BF9A685}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8895080" y="19333845"/>
+          <a:ext cx="2891790" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2296160</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>186690</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>186690</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="直線接點 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4152FD7A-528B-77B2-79B2-11D40C53F899}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3083560" y="23529290"/>
+          <a:ext cx="2891790" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1981200</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>46990</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="直線接點 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD2492FE-AFED-EA4E-9C10-54C20E6D5B4F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2768600" y="7086600"/>
+          <a:ext cx="2891790" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>481061</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="clip_image001.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="101600" y="0"/>
+          <a:ext cx="6354233" cy="673485"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40dd-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>481061</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="clip_image001.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="101600" y="0"/>
+          <a:ext cx="6362700" cy="671561"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40dd-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns="">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2184,502 +3759,606 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9988F256-56D9-452C-B565-0EB3F4CA4FF8}">
   <sheetPr>
     <tabColor theme="0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
   <cols>
-    <col width="10.33203125" customWidth="1" style="125" min="1" max="1"/>
-    <col width="43.6640625" customWidth="1" style="92" min="2" max="2"/>
-    <col width="14.83203125" customWidth="1" style="92" min="3" max="3"/>
-    <col width="8" customWidth="1" style="92" min="4" max="4"/>
-    <col width="9.33203125" customWidth="1" style="125" min="5" max="5"/>
-    <col width="5.5" customWidth="1" style="125" min="6" max="6"/>
-    <col width="17.1640625" customWidth="1" style="125" min="7" max="7"/>
-    <col width="8.83203125" customWidth="1" style="125" min="8" max="8"/>
-    <col width="6.1640625" bestFit="1" customWidth="1" style="125" min="9" max="9"/>
-    <col width="16" customWidth="1" style="125" min="10" max="10"/>
-    <col width="20.6640625" customWidth="1" style="125" min="11" max="11"/>
-    <col width="14.6640625" customWidth="1" style="125" min="12" max="12"/>
-    <col width="17.6640625" customWidth="1" style="125" min="13" max="13"/>
-    <col width="15.33203125" bestFit="1" customWidth="1" style="125" min="14" max="14"/>
-    <col width="12.1640625" customWidth="1" style="125" min="15" max="15"/>
-    <col width="9.1640625" bestFit="1" customWidth="1" style="125" min="16" max="16"/>
-    <col width="9.33203125" bestFit="1" customWidth="1" style="125" min="17" max="17"/>
-    <col width="9.1640625" bestFit="1" customWidth="1" style="125" min="18" max="18"/>
-    <col width="8" customWidth="1" style="125" min="19" max="19"/>
-    <col width="13.1640625" customWidth="1" style="125" min="20" max="20"/>
-    <col width="8.83203125" customWidth="1" style="125" min="21" max="16384"/>
+    <col min="1" max="1" width="10.33203125" style="91" customWidth="1"/>
+    <col min="2" max="2" width="43.6640625" style="92" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" style="92" customWidth="1"/>
+    <col min="4" max="4" width="8" style="92" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="91" customWidth="1"/>
+    <col min="6" max="6" width="5.5" style="91" customWidth="1"/>
+    <col min="7" max="7" width="17.1640625" style="91" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" style="91"/>
+    <col min="9" max="9" width="6.1640625" style="91" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" style="91" customWidth="1"/>
+    <col min="11" max="11" width="20.6640625" style="91" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" style="91" customWidth="1"/>
+    <col min="13" max="13" width="17.6640625" style="91" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" style="91" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1640625" style="91" customWidth="1"/>
+    <col min="16" max="16" width="9.1640625" style="91" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" style="91" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.1640625" style="91" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8" style="91" customWidth="1"/>
+    <col min="20" max="20" width="13.1640625" style="91" customWidth="1"/>
+    <col min="21" max="16384" width="8.83203125" style="91"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1"/>
-    <row r="2" ht="52.5" customHeight="1">
-      <c r="H2" s="92" t="n"/>
-      <c r="I2" s="92" t="n"/>
-      <c r="J2" s="92" t="n"/>
+    <row r="1" spans="1:14" ht="48" customHeight="1"/>
+    <row r="2" spans="1:14" ht="52.5" customHeight="1"/>
+    <row r="3" spans="1:14" ht="14" customHeight="1"/>
+    <row r="4" spans="1:14" ht="23">
+      <c r="A4" s="126" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="126"/>
+      <c r="G4" s="126"/>
     </row>
-    <row r="3" ht="14" customHeight="1">
-      <c r="H3" s="92" t="n"/>
-      <c r="I3" s="92" t="n"/>
-      <c r="J3" s="92" t="n"/>
-    </row>
-    <row r="4" ht="23" customHeight="1">
-      <c r="A4" s="126" t="inlineStr">
-        <is>
-          <t>********** 估    價    單 **********</t>
-        </is>
-      </c>
-      <c r="H4" s="92" t="n"/>
-      <c r="I4" s="92" t="n"/>
-      <c r="J4" s="92" t="n"/>
-    </row>
-    <row r="5" ht="21" customHeight="1">
-      <c r="A5" s="130" t="inlineStr">
-        <is>
-          <t>致       ：</t>
-        </is>
+    <row r="5" spans="1:14" ht="21" customHeight="1">
+      <c r="A5" s="101" t="s">
+        <v>155</v>
       </c>
       <c r="B5" s="102" t="inlineStr">
         <is>
-          <t>{{CLIENT_NAME}}</t>
+          <t xml:space="preserve">{{CLIENT_NAME}}</t>
         </is>
       </c>
-      <c r="C5" s="102" t="n"/>
-      <c r="D5" s="102" t="n"/>
-      <c r="E5" s="103" t="inlineStr">
-        <is>
-          <t>TEL：</t>
-        </is>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="103" t="s">
+        <v>153</v>
       </c>
       <c r="F5" s="130" t="inlineStr">
         <is>
-          <t>{{CLIENT_TEL}}</t>
+          <t xml:space="preserve">{{CLIENT_TEL}}</t>
         </is>
       </c>
-      <c r="H5" s="92" t="n"/>
-      <c r="I5" s="92" t="n"/>
-      <c r="J5" s="92" t="n"/>
+      <c r="G5" s="130"/>
     </row>
-    <row r="6" ht="21" customHeight="1">
-      <c r="A6" s="130" t="inlineStr">
-        <is>
-          <t>聯絡人：</t>
-        </is>
+    <row r="6" spans="1:14" ht="21" customHeight="1">
+      <c r="A6" s="101" t="s">
+        <v>141</v>
       </c>
       <c r="B6" s="102" t="inlineStr">
         <is>
-          <t>{{CONTACT}}</t>
+          <t xml:space="preserve">{{CONTACT}}</t>
         </is>
       </c>
-      <c r="C6" s="102" t="n"/>
-      <c r="D6" s="102" t="n"/>
-      <c r="E6" s="103" t="inlineStr">
-        <is>
-          <t>FAX：</t>
-        </is>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="103" t="s">
+        <v>159</v>
       </c>
-      <c r="F6" s="130" t="n"/>
-      <c r="H6" s="92" t="n"/>
-      <c r="I6" s="92" t="n"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130"/>
     </row>
-    <row r="7" ht="21" customHeight="1">
-      <c r="A7" s="130" t="inlineStr">
-        <is>
-          <t>估價編號：</t>
-        </is>
+    <row r="7" spans="1:14" ht="21" customHeight="1">
+      <c r="A7" s="101" t="s">
+        <v>142</v>
       </c>
       <c r="B7" s="120" t="inlineStr">
         <is>
-          <t>{{QUOTE_NO}}</t>
+          <t xml:space="preserve">{{QUOTE_NO}}</t>
         </is>
       </c>
-      <c r="E7" s="103" t="n"/>
-      <c r="H7" s="92" t="n"/>
-      <c r="I7" s="92" t="n"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="103"/>
     </row>
-    <row r="8" ht="21" customHeight="1">
-      <c r="A8" s="130" t="inlineStr">
-        <is>
-          <t>估價日期：</t>
-        </is>
+    <row r="8" spans="1:14" ht="21" customHeight="1">
+      <c r="A8" s="101" t="s">
+        <v>154</v>
       </c>
       <c r="B8" s="121" t="inlineStr">
         <is>
-          <t>{{QUOTE_DATE}}</t>
+          <t xml:space="preserve">{{QUOTE_DATE}}</t>
         </is>
       </c>
-      <c r="E8" s="103" t="n"/>
-      <c r="F8" s="130" t="n"/>
-      <c r="H8" s="92" t="n"/>
-      <c r="I8" s="92" t="n"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="130"/>
     </row>
-    <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="130" t="inlineStr">
-        <is>
-          <t>有效日期：</t>
-        </is>
+    <row r="9" spans="1:14" ht="21" customHeight="1">
+      <c r="A9" s="101" t="s">
+        <v>156</v>
       </c>
       <c r="B9" s="121" t="inlineStr">
         <is>
-          <t>{{VALID_DATE}}</t>
+          <t xml:space="preserve">{{VALID_DATE}}</t>
         </is>
       </c>
-      <c r="E9" s="103" t="n"/>
-      <c r="F9" s="131" t="n"/>
-      <c r="H9" s="92" t="n"/>
-      <c r="I9" s="92" t="n"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="131"/>
+      <c r="G9" s="131"/>
     </row>
-    <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="130" t="inlineStr">
-        <is>
-          <t>承辦業務：</t>
-        </is>
+    <row r="10" spans="1:14" ht="21" customHeight="1">
+      <c r="A10" s="101" t="s">
+        <v>157</v>
       </c>
-      <c r="B10" s="121" t="inlineStr">
-        <is>
-          <t>陳品伃</t>
-        </is>
+      <c r="B10" s="121" t="s">
+        <v>174</v>
       </c>
-      <c r="E10" s="103" t="inlineStr">
-        <is>
-          <t>TEL：</t>
-        </is>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="103" t="s">
+        <v>153</v>
       </c>
-      <c r="F10" s="130" t="inlineStr">
-        <is>
-          <t>02-26582223#113</t>
-        </is>
+      <c r="F10" s="130" t="s">
+        <v>176</v>
       </c>
-      <c r="H10" s="92" t="n"/>
-      <c r="I10" s="92" t="n"/>
+      <c r="G10" s="130"/>
     </row>
-    <row r="11" ht="21" customHeight="1" thickBot="1">
-      <c r="A11" s="130" t="inlineStr">
-        <is>
-          <t>E-Mail   ：</t>
-        </is>
+    <row r="11" spans="1:14" ht="21" customHeight="1" thickBot="1">
+      <c r="A11" s="101" t="s">
+        <v>158</v>
       </c>
-      <c r="B11" s="129" t="inlineStr">
-        <is>
-          <t>emilychen@flysheet.com.tw</t>
-        </is>
+      <c r="B11" s="129" t="s">
+        <v>175</v>
       </c>
-      <c r="E11" s="103" t="inlineStr">
-        <is>
-          <t>FAX：</t>
-        </is>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="103" t="s">
+        <v>159</v>
       </c>
-      <c r="F11" s="130" t="n"/>
-      <c r="H11" s="92" t="n"/>
-      <c r="I11" s="92" t="n"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="130"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="123" t="inlineStr">
-        <is>
-          <t>項次</t>
-        </is>
+    <row r="12" spans="1:14" ht="20" customHeight="1">
+      <c r="A12" s="107" t="s">
+        <v>143</v>
       </c>
-      <c r="B12" s="123" t="inlineStr">
-        <is>
-          <t>品名</t>
-        </is>
+      <c r="B12" s="123" t="s">
+        <v>160</v>
       </c>
-      <c r="C12" s="223" t="n"/>
-      <c r="D12" s="123" t="inlineStr">
-        <is>
-          <t>數量</t>
-        </is>
+      <c r="C12" s="123"/>
+      <c r="D12" s="107" t="s">
+        <v>149</v>
       </c>
-      <c r="E12" s="123" t="inlineStr">
-        <is>
-          <t>單位</t>
-        </is>
+      <c r="E12" s="107" t="s">
+        <v>150</v>
       </c>
-      <c r="F12" s="132" t="inlineStr">
-        <is>
-          <t>總價</t>
-        </is>
+      <c r="F12" s="132" t="s">
+        <v>147</v>
       </c>
-      <c r="G12" s="223" t="n"/>
-      <c r="J12" s="125" t="n"/>
-      <c r="L12" s="94" t="n"/>
-      <c r="M12" s="94" t="n"/>
+      <c r="G12" s="132"/>
     </row>
-    <row r="13">
-      <c r="A13" s="111" t="n">
+    <row r="13" spans="1:14">
+      <c r="A13" s="111">
         <v>1</v>
       </c>
       <c r="B13" s="122" t="inlineStr">
         <is>
-          <t>{{PRODUCT}}</t>
+          <t xml:space="preserve">{{PRODUCT}}</t>
         </is>
       </c>
-      <c r="C13" s="224" t="n"/>
-      <c r="D13" s="112" t="n"/>
-      <c r="E13" s="225" t="n"/>
-      <c r="F13" s="225" t="n">
+      <c r="C13" s="122"/>
+      <c r="D13" s="112"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="133">
         <v>999999901</v>
       </c>
-      <c r="K13" s="226" t="n"/>
-      <c r="L13" s="226" t="n"/>
-      <c r="M13" s="226" t="n"/>
-      <c r="N13" s="226" t="n"/>
+      <c r="G13" s="133"/>
     </row>
-    <row r="14" ht="43" customFormat="1" customHeight="1" s="92">
-      <c r="A14" s="106" t="n"/>
+    <row r="14" spans="1:14" s="92" customFormat="1" ht="43" customHeight="1">
+      <c r="A14" s="106"/>
       <c r="B14" s="134" t="inlineStr">
         <is>
-          <t>訂期：{{PERIOD}}</t>
+          <t xml:space="preserve">訂期：{{PERIOD}}</t>
         </is>
       </c>
-      <c r="D14" s="134" t="n"/>
-      <c r="E14" s="227" t="n"/>
-      <c r="F14" s="227" t="n"/>
-      <c r="K14" s="228" t="n"/>
-      <c r="L14" s="228" t="n"/>
-      <c r="M14" s="228" t="n"/>
-      <c r="N14" s="228" t="n"/>
+      <c r="C14" s="134"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
     </row>
-    <row r="15" ht="21" customFormat="1" customHeight="1" s="92">
-      <c r="A15" s="106" t="n"/>
-      <c r="B15" s="134" t="n"/>
-      <c r="D15" s="134" t="n"/>
-      <c r="E15" s="227" t="n"/>
-      <c r="F15" s="227" t="n"/>
-      <c r="K15" s="228" t="n"/>
-      <c r="L15" s="228" t="n"/>
-      <c r="M15" s="228" t="n"/>
-      <c r="N15" s="228" t="n"/>
+    <row r="15" spans="1:14" s="92" customFormat="1" ht="21" customHeight="1">
+      <c r="A15" s="106"/>
+      <c r="B15" s="134"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119"/>
     </row>
-    <row r="16" ht="21" customFormat="1" customHeight="1" s="92">
-      <c r="A16" s="106" t="n"/>
-      <c r="B16" s="134" t="n"/>
-      <c r="D16" s="134" t="n"/>
-      <c r="E16" s="227" t="n"/>
-      <c r="F16" s="227" t="n"/>
-      <c r="K16" s="228" t="n"/>
-      <c r="L16" s="228" t="n"/>
-      <c r="M16" s="228" t="n"/>
-      <c r="N16" s="228" t="n"/>
+    <row r="16" spans="1:14" s="92" customFormat="1" ht="21" customHeight="1">
+      <c r="A16" s="106"/>
+      <c r="B16" s="134"/>
+      <c r="C16" s="134"/>
+      <c r="D16" s="104"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
     </row>
-    <row r="17" ht="25" customHeight="1" thickBot="1">
-      <c r="A17" s="108" t="n"/>
-      <c r="B17" s="124" t="n"/>
-      <c r="C17" s="229" t="n"/>
-      <c r="D17" s="124" t="n"/>
-      <c r="E17" s="110" t="n"/>
-      <c r="F17" s="230" t="n"/>
-      <c r="G17" s="229" t="n"/>
-      <c r="H17" s="97" t="n"/>
-      <c r="K17" s="231" t="n"/>
-      <c r="L17" s="231" t="n"/>
-      <c r="M17" s="231" t="n"/>
-      <c r="N17" s="231" t="n"/>
-      <c r="O17" s="231" t="n"/>
-      <c r="P17" s="231" t="n"/>
-      <c r="Q17" s="231" t="n"/>
-      <c r="R17" s="231" t="n"/>
-      <c r="S17" s="231" t="n"/>
+    <row r="17" spans="1:19" ht="25" customHeight="1" thickBot="1">
+      <c r="A17" s="108"/>
+      <c r="B17" s="124"/>
+      <c r="C17" s="124"/>
+      <c r="D17" s="109"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="118"/>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="127" t="inlineStr">
-        <is>
-          <t>總價(含稅)：</t>
-        </is>
+    <row r="18" spans="1:19" ht="24" customHeight="1">
+      <c r="A18" s="127" t="s">
+        <v>145</v>
       </c>
-      <c r="F18" s="227">
+      <c r="B18" s="127"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="127"/>
+      <c r="E18" s="128"/>
+      <c r="F18" s="119">
         <f>SUM(F13:G17)</f>
-        <v/>
+        <v>25000</v>
+      </c>
+      <c r="G18" s="119"/>
+    </row>
+    <row r="20" spans="1:19" ht="19">
+      <c r="B20" s="116" t="s">
+        <v>161</v>
+      </c>
+      <c r="C20" s="117">
+        <f>F18</f>
+        <v>25000</v>
+      </c>
+      <c r="D20" s="115" t="s">
+        <v>162</v>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20" ht="19" customHeight="1">
-      <c r="B20" s="116" t="inlineStr">
-        <is>
-          <t>總金額： 新台幣</t>
-        </is>
-      </c>
-      <c r="C20" s="232">
-        <f>F18</f>
-        <v/>
-      </c>
-      <c r="D20" s="115" t="inlineStr">
-        <is>
-          <t>元整</t>
-        </is>
+    <row r="21" spans="1:19">
+      <c r="B21" s="114"/>
+      <c r="C21" s="114"/>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" s="93" t="s">
+        <v>144</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="114" t="n"/>
-      <c r="C21" s="114" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="127" t="inlineStr">
-        <is>
-          <t>備註：</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="125" t="n">
+    <row r="23" spans="1:19" ht="19">
+      <c r="A23" s="91">
         <v>1</v>
       </c>
       <c r="B23" s="100" t="inlineStr">
         <is>
-          <t>{{NOTE1}}</t>
+          <t xml:space="preserve">{{NOTE1}}</t>
         </is>
       </c>
-      <c r="C23" s="100" t="n"/>
-      <c r="D23" s="100" t="n"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="100"/>
     </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="125" t="n">
-        <v>2</v>
+    <row r="24" spans="1:19" ht="19">
+      <c r="A24" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{NOTE2_NUM}}</t>
+        </is>
       </c>
       <c r="B24" s="100" t="inlineStr">
         <is>
-          <t>{{NOTE2}}</t>
+          <t xml:space="preserve">{{NOTE2}}</t>
         </is>
       </c>
-      <c r="C24" s="100" t="n"/>
-      <c r="D24" s="100" t="n"/>
+      <c r="C24" s="100"/>
+      <c r="D24" s="100"/>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="100" t="inlineStr">
-        <is>
-          <t>{{NOTE3}}</t>
-        </is>
-      </c>
-      <c r="C25" s="100" t="n"/>
-      <c r="D25" s="100" t="n"/>
+    <row r="25" spans="1:19">
+      <c r="B25" s="100"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="100"/>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" s="125" t="inlineStr">
-        <is>
-          <t>{{NOTE4}}</t>
-        </is>
-      </c>
-      <c r="C26" s="125" t="n"/>
-      <c r="D26" s="100" t="n"/>
+    <row r="26" spans="1:19">
+      <c r="B26" s="91"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="100"/>
     </row>
-    <row r="27">
-      <c r="B27" s="100" t="n"/>
-      <c r="C27" s="100" t="n"/>
-      <c r="D27" s="100" t="n"/>
+    <row r="27" spans="1:19">
+      <c r="B27" s="100"/>
+      <c r="C27" s="100"/>
+      <c r="D27" s="100"/>
     </row>
-    <row r="28" customFormat="1" s="231">
-      <c r="A28" s="125" t="n"/>
-      <c r="B28" s="92" t="n"/>
-      <c r="C28" s="92" t="n"/>
-      <c r="D28" s="92" t="n"/>
-      <c r="E28" s="125" t="n"/>
-      <c r="H28" s="125" t="n"/>
-      <c r="I28" s="125" t="n"/>
-      <c r="J28" s="125" t="n"/>
-      <c r="K28" s="125" t="n"/>
-      <c r="L28" s="125" t="n"/>
-      <c r="M28" s="125" t="n"/>
-      <c r="N28" s="125" t="n"/>
+    <row r="28" spans="1:19" s="99" customFormat="1">
+      <c r="A28" s="91"/>
+      <c r="B28" s="92"/>
+      <c r="C28" s="92"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="125"/>
+      <c r="G28" s="125"/>
     </row>
-    <row r="29" customFormat="1" s="231">
-      <c r="A29" s="125" t="n"/>
-      <c r="B29" s="92" t="n"/>
-      <c r="C29" s="92" t="n"/>
-      <c r="D29" s="92" t="n"/>
-      <c r="E29" s="125" t="n"/>
-      <c r="H29" s="125" t="n"/>
-      <c r="I29" s="125" t="n"/>
-      <c r="J29" s="125" t="n"/>
-      <c r="K29" s="125" t="n"/>
-      <c r="L29" s="125" t="n"/>
-      <c r="M29" s="125" t="n"/>
-      <c r="N29" s="125" t="n"/>
+    <row r="29" spans="1:19" s="99" customFormat="1">
+      <c r="A29" s="91"/>
+      <c r="B29" s="92"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="125"/>
+      <c r="F29" s="125"/>
+      <c r="G29" s="125"/>
     </row>
-    <row r="30" customFormat="1" s="231">
-      <c r="A30" s="125" t="n"/>
-      <c r="B30" s="92" t="n"/>
-      <c r="C30" s="92" t="n"/>
-      <c r="D30" s="92" t="n"/>
-      <c r="E30" s="125" t="n"/>
-      <c r="H30" s="125" t="n"/>
-      <c r="I30" s="125" t="n"/>
-      <c r="J30" s="125" t="n"/>
-      <c r="K30" s="125" t="n"/>
-      <c r="L30" s="125" t="n"/>
-      <c r="M30" s="125" t="n"/>
-      <c r="N30" s="125" t="n"/>
+    <row r="30" spans="1:19" s="99" customFormat="1">
+      <c r="A30" s="91"/>
+      <c r="B30" s="92"/>
+      <c r="C30" s="92"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="125"/>
+      <c r="F30" s="125"/>
+      <c r="G30" s="125"/>
     </row>
-    <row r="31" customFormat="1" s="231">
-      <c r="A31" s="125" t="n"/>
-      <c r="B31" s="92" t="n"/>
-      <c r="C31" s="92" t="n"/>
-      <c r="D31" s="92" t="n"/>
-      <c r="E31" s="125" t="n"/>
-      <c r="F31" s="125" t="n"/>
-      <c r="G31" s="125" t="n"/>
-      <c r="H31" s="125" t="n"/>
-      <c r="I31" s="125" t="n"/>
-      <c r="J31" s="125" t="n"/>
-      <c r="K31" s="125" t="n"/>
-      <c r="L31" s="125" t="n"/>
-      <c r="M31" s="125" t="n"/>
-      <c r="N31" s="125" t="n"/>
+    <row r="31" spans="1:19" s="99" customFormat="1">
+      <c r="A31" s="91"/>
+      <c r="B31" s="92"/>
+      <c r="C31" s="92"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="91"/>
+      <c r="F31" s="91"/>
+      <c r="G31" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="B10:D10"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F8:G8"/>
     <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F14:G14"/>
     <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="E29:G29"/>
   </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId1"/>
+    <hyperlink ref="B11" r:id="rId1" xr:uid="{AE8BBA1D-2E3B-4E31-85DC-54CA10D318DF}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3543307086614174" right="0.3149606299212598" top="0.6692913385826772" bottom="0.3543307086614174" header="0.1968503937007874" footer="0.1574803149606299"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="83" fitToHeight="0"/>
+  <pageMargins left="0.35433070866141736" right="0.31496062992125984" top="0.6692913385826772" bottom="0.35433070866141736" header="0.19685039370078741" footer="0.15748031496062992"/>
+  <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="portrait" r:id="rId2"/>
   <headerFooter alignWithMargins="0">
-    <oddHeader>&amp;C_x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a__x000a_&amp;G</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
+    <oddHeader>&amp;C
+&amp;G</oddHeader>
   </headerFooter>
+  <drawing r:id="rId3"/>
+  <legacyDrawingHF r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:XFD35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="47" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <mergeCells count="12">
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="D7:D14"/>
+    <mergeCell ref="E7:E14"/>
+    <mergeCell ref="E24:E33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="E16:E23"/>
+    <mergeCell ref="D16:D23"/>
+    <mergeCell ref="C16:C23"/>
+    <mergeCell ref="C24:C33"/>
+    <mergeCell ref="D24:D33"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A4:P26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.1640625" customWidth="1"/>
+    <col min="3" max="3" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="5.5" customWidth="1"/>
+    <col min="11" max="11" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <mergeCells count="15">
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="K6:K13"/>
+    <mergeCell ref="K15:K17"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="M6:M13"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="M18:M25"/>
+    <mergeCell ref="K18:K25"/>
+    <mergeCell ref="C26:I26"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:XFD35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="47" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <mergeCells count="12">
+    <mergeCell ref="C24:C33"/>
+    <mergeCell ref="D24:D33"/>
+    <mergeCell ref="E24:E33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D7:D14"/>
+    <mergeCell ref="E7:E14"/>
+    <mergeCell ref="C16:C23"/>
+    <mergeCell ref="D16:D23"/>
+    <mergeCell ref="E16:E23"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:O39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="48.33203125" customWidth="1"/>
+    <col min="12" max="12" width="11.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <mergeCells count="47">
+    <mergeCell ref="C39:I39"/>
+    <mergeCell ref="J35:J38"/>
+    <mergeCell ref="I35:I38"/>
+    <mergeCell ref="H35:H38"/>
+    <mergeCell ref="G35:G38"/>
+    <mergeCell ref="F35:F38"/>
+    <mergeCell ref="E35:E38"/>
+    <mergeCell ref="D35:D38"/>
+    <mergeCell ref="C35:C38"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="J25:J29"/>
+    <mergeCell ref="I25:I29"/>
+    <mergeCell ref="H25:H29"/>
+    <mergeCell ref="G25:G29"/>
+    <mergeCell ref="F25:F29"/>
+    <mergeCell ref="E25:E29"/>
+    <mergeCell ref="D25:D29"/>
+    <mergeCell ref="C25:C29"/>
+    <mergeCell ref="A25:A29"/>
+    <mergeCell ref="K24:K38"/>
+    <mergeCell ref="J17:J22"/>
+    <mergeCell ref="I17:I22"/>
+    <mergeCell ref="H17:H22"/>
+    <mergeCell ref="G17:G22"/>
+    <mergeCell ref="J10:J14"/>
+    <mergeCell ref="I10:I14"/>
+    <mergeCell ref="H10:H14"/>
+    <mergeCell ref="G10:G14"/>
+    <mergeCell ref="F10:F14"/>
+    <mergeCell ref="E17:E22"/>
+    <mergeCell ref="D17:D22"/>
+    <mergeCell ref="C17:C22"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="K16:K23"/>
+    <mergeCell ref="F17:F22"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="E10:E14"/>
+    <mergeCell ref="D10:D14"/>
+    <mergeCell ref="C10:C14"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="C1:C2"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetData/>
+  <mergeCells count="4">
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A32:A35"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetData/>
+  <mergeCells count="16">
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A6:A12"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="I1:I4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>